--- a/daily_matches/job_matches_2026-08-06.xlsx
+++ b/daily_matches/job_matches_2026-08-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, FastAPI, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aff60950e630b6e3</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4b33ddd29938b6</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI/ML ENG III</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fujitsu</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, Synapse, Git, Snowflake, Databricks</t>
+          <t>Data Scientist, LangChain, RAG, Copilot, Kubernetes, CI/CD, Git, Snowflake, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c79fecb88f759cdc</t>
+          <t>https://www.indeed.com/viewjob?jk=8fb3264f58d94550</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Internal Applications Engineer - Network Evolution</t>
+          <t>Full Stack SaaS development</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bandwidth</t>
+          <t>osp labs hiring for us based mnc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, FastAPI, Docker, Git, Snowflake, Python, SQL, R</t>
+          <t>RAG, Athena, FastAPI, Docker, Kubernetes, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ba8965e92ec2146</t>
+          <t>https://www.indeed.com/viewjob?jk=70ba9d56baa5b97e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, PyTorch, Docker, Kubernetes, AKS, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, CI/CD, Git, Kafka, MongoDB, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10322f033b271931</t>
+          <t>https://www.indeed.com/viewjob?jk=b8b790018e6435ce</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Software Engineer (Austin)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ketch</t>
+          <t>State of Texas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Git, Cassandra, Python, R, Java, Scala</t>
+          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5d2c1be2dfe526</t>
+          <t>https://www.indeed.com/viewjob?jk=e975d446e8ff42a3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer III - Platform Data Engineer (Remote)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Apache Airflow, CI/CD, Terraform, Python, SQL, R, Scala</t>
+          <t>RAG, CI/CD, Git, Kafka, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93749d43fe3ef5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=a80d9ad7a8d34ffe</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wisetek Providers Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dunn Loring, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, CI/CD, Databricks, Hadoop, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,252 +706,77 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72a7ee4a1788e71</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fee6ae5cd1f5ae</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Java Full Stack Software Engineer III - React / Kubernetes</t>
+          <t>Senior Data Analytics and Research Analyst</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Git, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d398f3f362c8511c</t>
+          <t>https://www.indeed.com/viewjob?jk=05b634294d1ddbff</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Java Full Stack Software Engineer III - React / PostgreSQL</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Copilot, Docker, Git, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5098c1122253111e</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>CLERA</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ce11b9433c91a10</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Software Engineer III NA</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Robert Half</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>San Ramon, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1235d9f4df7b10e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>AI Network Automation Engineer intern (Global Physical Network Infra) - 2027 Summer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ByteDance</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, CI/CD, NoSQL, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=78d38c8ca2e45b9d</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Java Backend Software Engineer II - Spring Boot</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8618671a2ad8c996</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Data Science Product Senior Associate</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Newark, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Databricks, Python, SQL, R, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8516e76ab15f7bd</t>
+          <t>https://www.indeed.com/viewjob?jk=585c50155b96f458</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-06.xlsx
+++ b/daily_matches/job_matches_2026-08-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI / Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Celebration, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, FastAPI, CI/CD, Terraform, Git, Python</t>
+          <t>RAG, S3, Glue, Kinesis, Docker, CI/CD, Jenkins, Git, Snowflake, MongoDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,19 +496,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4b33ddd29938b6</t>
+          <t>https://www.indeed.com/viewjob?jk=4a1d158814d4803d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Monogram Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,46 +517,46 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Copilot, Kubernetes, CI/CD, Git, Snowflake, MongoDB, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Azure ML, MLflow, Docker, CI/CD, GitHub Actions, Git, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fb3264f58d94550</t>
+          <t>https://www.indeed.com/viewjob?jk=4fe0dee1e8474ed0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack SaaS development</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>osp labs hiring for us based mnc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Athena, FastAPI, Docker, Kubernetes, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>LangChain, RAG, LLaMA, Copilot, Docker, AKS, CI/CD, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70ba9d56baa5b97e</t>
+          <t>https://www.indeed.com/viewjob?jk=d45dda7076140234</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Azure ETL Architect – Data Modernization</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Cyberlocke, LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Kafka, MongoDB, SQL, R, Java, Scala, Optimization</t>
+          <t>Synapse, Data Lake, Dataflow, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8b790018e6435ce</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb3d2789d2f0f62</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer (Austin)</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>State of Texas</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, R, Java</t>
+          <t>Generative AI, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e975d446e8ff42a3</t>
+          <t>https://www.indeed.com/viewjob?jk=66c02e32222a87e9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Solutions Architect, Financial Services Banking</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Kafka, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, Git, Dask, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a80d9ad7a8d34ffe</t>
+          <t>https://www.indeed.com/viewjob?jk=42163340e8aafdd1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, Git, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fee6ae5cd1f5ae</t>
+          <t>https://www.indeed.com/viewjob?jk=ce05553d6f687dc8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Analytics and Research Analyst</t>
+          <t>Senior Software Engineer - Integrations - AI/ML</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Kafka, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b634294d1ddbff</t>
+          <t>https://www.indeed.com/viewjob?jk=828c2593dd3b6144</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>FourKites</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,17 +766,157 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Docker, Git, MongoDB, Python, SQL, R</t>
+          <t>LangChain, RAG, Prompt Engineering, AKS, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=585c50155b96f458</t>
+          <t>https://www.indeed.com/viewjob?jk=3a5afc66ccf1e5f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer Insurance Domain &amp; Data Background</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Innovative Tech Solutions</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Hadoop, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aebfdc3116bf7f46</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DevOps Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Delta Dental</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=895a525d84abad93</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sr MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Intuitive (Intuitive Surgical)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, S3, MLflow, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=679a21efc0a0f190</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CNC-Spezialist</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mettler-Toledo</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Terraform, Git, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f23c9bacd82bf38</t>
         </is>
       </c>
     </row>
